--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiss\OneDrive\Documentos\GitHub\ChecklistVehiculo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TRABAJO\PROGRAMA\ChecklistVehiculo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11DE996F-9FBA-4CA4-9372-48F1A3E16440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAE1F4D-FB15-44B8-B451-A19BC092FDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-1980" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3F19E3F8-0C11-4B53-83B5-0D783A364708}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{3F19E3F8-0C11-4B53-83B5-0D783A364708}"/>
   </bookViews>
   <sheets>
     <sheet name="Contratos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Codigo</t>
   </si>
@@ -54,18 +54,6 @@
     <t>FTO-AL101XX-26</t>
   </si>
   <si>
-    <t>PRUEBA DE CONTRATO 1</t>
-  </si>
-  <si>
-    <t>PRUEBA DE CONTRATO 2</t>
-  </si>
-  <si>
-    <t>PRUEBA DE CONTRATO 3</t>
-  </si>
-  <si>
-    <t>PRUEBA DE CONTRATO 4</t>
-  </si>
-  <si>
     <t>V2</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>ABCD-19</t>
   </si>
   <si>
-    <t>PRUEBA RESPONSABLE 1</t>
-  </si>
-  <si>
     <t>PRUEBA RESPONSABLE 2</t>
   </si>
   <si>
@@ -127,6 +112,30 @@
   </si>
   <si>
     <t>PRUEBA RESPONSABLE 8</t>
+  </si>
+  <si>
+    <t>FTO-AL10185-26</t>
+  </si>
+  <si>
+    <t>PRUEBA DE CONTRATO 85</t>
+  </si>
+  <si>
+    <t>PRUEBA DE CONTRATO 2985</t>
+  </si>
+  <si>
+    <t>PRUEBA DE CONTRATO 3456</t>
+  </si>
+  <si>
+    <t>PRUEBA DE CONTRATO 4456456</t>
+  </si>
+  <si>
+    <t>asdasdasdasdas</t>
+  </si>
+  <si>
+    <t>KBSP-13</t>
+  </si>
+  <si>
+    <t>LUIS SEPULVEDA</t>
   </si>
 </sst>
 </file>
@@ -174,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -197,16 +206,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -564,10 +587,10 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -578,10 +601,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -589,10 +612,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -600,10 +623,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E5E18B0-6A0A-44FB-8753-FE021DE733A8}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -622,74 +645,82 @@
   <sheetData>
     <row r="1" spans="1:2" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
